--- a/Final Report/Relatorio_Controle_Trocas.xlsx
+++ b/Final Report/Relatorio_Controle_Trocas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U136"/>
+  <dimension ref="A1:U138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -752,7 +752,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ICL America do Sul S.A</t>
+          <t>MOSAIC FERTILIZANTES BRASIL LTDA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>60398138000546</t>
+          <t>00910509000171</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -813,7 +813,7 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
-          <t>MOSAIC FERTILIZANTES BRASIL LTDA</t>
+          <t>RODOFROTA TRANSP RODOVIARIOS LOGIST LTDA</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ICL America do Sul S.A</t>
+          <t>MOSAIC FERTILIZANTES BRASIL LTDA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>60398138000546</t>
+          <t>00910509000171</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -916,7 +916,7 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
-          <t>MOSAIC FERTILIZANTES BRASIL LTDA</t>
+          <t>RODOFROTA TRANSP RODOVIARIOS LOGIST LTDA</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1431,7 +1431,7 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
-          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA</t>
+          <t>TRANS CINCO TRANSPORTES RODOVIARIOS</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1534,7 +1534,7 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
-          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA</t>
+          <t>TRANS CINCO TRANSPORTES RODOVIARIOS</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1637,7 +1637,7 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
-          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA</t>
+          <t>TRANS CINCO TRANSPORTES RODOVIARIOS</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45960</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1740,7 +1740,7 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
-          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA II</t>
+          <t>TINDIANA LOGISTICA E TRANSPORTE LTDA</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>35830</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1843,7 +1843,7 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
-          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA II</t>
+          <t>TINDIANA LOGISTICA E TRANSPORTE LTDA</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>47480</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1946,7 +1946,7 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
         <is>
-          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA I</t>
+          <t>GRANLIDER TRANSPORTES E AGENCIAMENTOS DE CARGAS LTDA</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>47660</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2049,7 +2049,7 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
         <is>
-          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA I</t>
+          <t>GRANLIDER TRANSPORTES E AGENCIAMENTOS DE CARGAS LTDA</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2111,7 +2111,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>47460</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2152,7 +2152,7 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
         <is>
-          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA I</t>
+          <t>GRANLIDER TRANSPORTES E AGENCIAMENTOS DE CARGAS LTDA</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>35710</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2255,7 +2255,7 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
         <is>
-          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA II</t>
+          <t>TINDIANA LOGISTICA E TRANSPORTE LTDA</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17280</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2358,7 +2358,7 @@
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
         <is>
-          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA I</t>
+          <t>LOGIC TRANSPORTES EIRELI</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2420,7 +2420,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17740</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2461,7 +2461,7 @@
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
         <is>
-          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA I</t>
+          <t>LOGIC TRANSPORTES EIRELI</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>47560</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2564,7 +2564,7 @@
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
         <is>
-          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA I</t>
+          <t>GRANLIDER TRANSPORTES E AGENCIAMENTOS DE CARGAS LTDA</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>33420</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2667,7 +2667,7 @@
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
         <is>
-          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA I</t>
+          <t>TRANSCORONEL TRANSPORTES E LOGISTICA LTDA</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2832,7 +2832,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20520</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2873,7 +2873,7 @@
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
         <is>
-          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA I</t>
+          <t>TRANS-CINCO TRANSPORTES RODOVIARIOS LTDAEPP</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -2935,7 +2935,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>48860</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2976,7 +2976,7 @@
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
         <is>
-          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA I</t>
+          <t>GRANLIDER TRANSPORTES E AGENCIAMENTOS DE CARGAS LTDA</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>35610</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3079,7 +3079,7 @@
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
         <is>
-          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA II</t>
+          <t>TINDIANA LOGISTICA E TRANSPORTE LTDA</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>26020</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3182,7 +3182,7 @@
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
         <is>
-          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA I</t>
+          <t>TRANSCORONEL TRANSPORTES E LOGISTICA LTDA</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17540</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3388,7 +3388,7 @@
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
         <is>
-          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA I</t>
+          <t>LOGIC TRANSPORTES EIRELI</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15780</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3491,7 +3491,7 @@
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
         <is>
-          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA I</t>
+          <t>LOGIC TRANSPORTES EIRELI</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3553,7 +3553,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>46960</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3594,7 +3594,7 @@
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
         <is>
-          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA I</t>
+          <t>GRANLIDER TRANSPORTES E AGENCIAMENTOS DE CARGAS LTDA</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3656,7 +3656,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>49840</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3697,7 +3697,7 @@
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
         <is>
-          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA I</t>
+          <t>GRANLIDER TRANSPORTES E AGENCIAMENTOS DE CARGAS LTDA</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3759,7 +3759,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18460</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3800,7 +3800,7 @@
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
         <is>
-          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA I</t>
+          <t>LOGIC TRANSPORTES EIRELI</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>46830</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3903,7 +3903,7 @@
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
         <is>
-          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA II</t>
+          <t>TINDIANA LOGISTICA E TRANSPORTE LTDA</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16900</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4006,7 +4006,7 @@
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
         <is>
-          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA I</t>
+          <t>LOGIC TRANSPORTES EIRELI</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4212,7 +4212,7 @@
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr">
         <is>
-          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
+          <t>TRANSPORTADORA BOA VIAGEM LTDA</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4315,7 +4315,7 @@
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr">
         <is>
-          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
+          <t>TRANSPORTADORA BOA VIAGEM LTDA</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4418,7 +4418,7 @@
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr">
         <is>
-          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
+          <t>RODOFROTA TRANSPORTES RODOVIARIOS E LOGISTICA LTDA</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4521,7 +4521,7 @@
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr">
         <is>
-          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
+          <t>G10 TRANSPORTES S A</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -4624,7 +4624,7 @@
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr">
         <is>
-          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
+          <t>TRANSPORTADORA BOA VIAGEM LTDA</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>47430</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4727,7 +4727,7 @@
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr">
         <is>
-          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA II</t>
+          <t>TINDIANA LOGISTICA E TRANSPORTE LTDA</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45820</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>43331955191</t>
+          <t>05089654000157</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -4830,7 +4830,7 @@
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr">
         <is>
-          <t>DEISE LAINE ALVES</t>
+          <t>TINDIANA LOGISTICA E TRANSPORTES LTDA</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -4922,7 +4922,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>43331955191</t>
+          <t>05089654000157</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -4933,7 +4933,7 @@
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr">
         <is>
-          <t>DEISE LAINE ALVES</t>
+          <t>TINDIANA LOGISTICA E TRANSPORTES LTDA</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5036,7 +5036,7 @@
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr">
         <is>
-          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
+          <t>TRANSVAL TRANSPORTADORA VALMIR LTDA</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5139,7 +5139,7 @@
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr">
         <is>
-          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA</t>
+          <t>TRANS CINCO TRANSPORTES RODOVIARIOS</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -5304,7 +5304,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>46640</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5345,7 +5345,7 @@
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr">
         <is>
-          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA II</t>
+          <t>TINDIANA LOGISTICA E TRANSPORTE LTDA</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -5407,7 +5407,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>36</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5448,7 +5448,7 @@
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr">
         <is>
-          <t>AUTEM DO BRASIL LTDA</t>
+          <t>TRANS-CINCO TRANSP RODOVIARIOS LTDA</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -5510,7 +5510,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -5551,7 +5551,7 @@
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr">
         <is>
-          <t>AUTEM DO BRASIL LTDA</t>
+          <t>TRANS-CINCO TRANSP RODOVIARIOS LTDA</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -5613,7 +5613,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30780</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -5654,7 +5654,7 @@
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr">
         <is>
-          <t>BRONOVSKI COM DE SALVADOS LTDA</t>
+          <t>Mosaic Fertilizantes do Brasil Ltda</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -5716,7 +5716,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>49160</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -5757,7 +5757,7 @@
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr">
         <is>
-          <t>CTO 1 AGROPECUARIA S.A.</t>
+          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>47220</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -5860,7 +5860,7 @@
       <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr">
         <is>
-          <t>CTO 1 AGROPECUARIA S.A.</t>
+          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>46940</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -5963,7 +5963,7 @@
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr">
         <is>
-          <t>BOM FUTURO AGRICOLA LTDA</t>
+          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -6025,7 +6025,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>47360</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -6066,7 +6066,7 @@
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr">
         <is>
-          <t>CTO 1 AGROPECUARIA SA</t>
+          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>47420</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6169,7 +6169,7 @@
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr">
         <is>
-          <t>CTO 1 AGROPECUARIA SA</t>
+          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -6231,7 +6231,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>47820</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -6272,7 +6272,7 @@
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr">
         <is>
-          <t>CTO 1 AGROPECUARIA SA</t>
+          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -6334,7 +6334,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>48</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -6375,7 +6375,7 @@
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr">
         <is>
-          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
+          <t>FERTRAN TRANSPORTES LTDA</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -6478,7 +6478,7 @@
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr">
         <is>
-          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
+          <t>AGROLOG TRANSPORT CARGAS GERAL LTDA</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -6581,7 +6581,7 @@
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr">
         <is>
-          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
+          <t>BUDEL TRANSPORTES LTDA</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -6643,7 +6643,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>47400</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -6684,7 +6684,7 @@
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr">
         <is>
-          <t>CTO 1 AGROPECUARIA S.A.</t>
+          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>47440</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -6787,7 +6787,7 @@
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr">
         <is>
-          <t>CTO 1 AGROPECUARIA S.A.</t>
+          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
@@ -6849,7 +6849,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>46360</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -6890,7 +6890,7 @@
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr">
         <is>
-          <t>CTO 1 AGROPECUARIA S.A.</t>
+          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -6952,7 +6952,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>50100</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -6993,7 +6993,7 @@
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr">
         <is>
-          <t>BOM FUTURO AGRICOLA LTDA</t>
+          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
@@ -7055,7 +7055,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>49660</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -7096,7 +7096,7 @@
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr">
         <is>
-          <t>BOM FUTURO AGRICOLA LTDA</t>
+          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>25000</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -7199,7 +7199,7 @@
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr">
         <is>
-          <t>COONAGRO COOPERATIVA NACIONAL</t>
+          <t>DIVONSIR PRIEVE 02917886960</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
@@ -7261,7 +7261,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>48580</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -7302,7 +7302,7 @@
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr">
         <is>
-          <t>CTO 1 AGROPECUARIA SA</t>
+          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>49360</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -7405,7 +7405,7 @@
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr">
         <is>
-          <t>CTO 1 AGROPECUARIA SA</t>
+          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>1616000</t>
+          <t>800</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>800</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -7508,7 +7508,7 @@
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr">
         <is>
-          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA I</t>
+          <t>47059545 DIVONSIR PRIEVE</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
@@ -7570,7 +7570,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>48440</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -7611,7 +7611,7 @@
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr">
         <is>
-          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA I</t>
+          <t>GRANLIDER TRANSPORTES E AGENCIAMENTOS DE CARGAS LTDA</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
@@ -7673,7 +7673,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>46940</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -7714,7 +7714,7 @@
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr">
         <is>
-          <t>CTO 1 AGROPECUARIA S.A.</t>
+          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>48880</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -7817,7 +7817,7 @@
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr">
         <is>
-          <t>CTO 1 AGROPECUARIA S.A.</t>
+          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
@@ -7879,7 +7879,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>47800</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -7920,7 +7920,7 @@
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr">
         <is>
-          <t>CTO 1 AGROPECUARIA S.A.</t>
+          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
@@ -8023,7 +8023,7 @@
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr">
         <is>
-          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
+          <t>RODOFROTA TRANSPORTES RODOVIARIOS E LOGISTICA LTDA</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>48100</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -8126,7 +8126,7 @@
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr">
         <is>
-          <t>CTO 1 AGROPECUARIA S.A.</t>
+          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
@@ -8188,7 +8188,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>47740</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -8229,7 +8229,7 @@
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr">
         <is>
-          <t>CTO 1 AGROPECUARIA SA</t>
+          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
@@ -8291,7 +8291,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>46400</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -8332,7 +8332,7 @@
       <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr">
         <is>
-          <t>BOM FUTURO AGRICOLA LTDA</t>
+          <t>RODOPAR TRANSPORTES RODOVIARIOS LTD RODOPAR TRANSPORTES RODO</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
@@ -8394,7 +8394,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>47200</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -8435,7 +8435,7 @@
       <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr">
         <is>
-          <t>CTO 1 AGROPECUARIA S.A.</t>
+          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
@@ -8538,7 +8538,7 @@
       <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr">
         <is>
-          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
+          <t>RODO M LOGISTICA E SERVICOS LTDA</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
@@ -8600,7 +8600,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>46400</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -8641,7 +8641,7 @@
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr">
         <is>
-          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
+          <t>TRANSVAL TRANSPORTADORA VALMIR LTDA</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
@@ -8703,7 +8703,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31590</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -8744,7 +8744,7 @@
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr">
         <is>
-          <t>BRONOVSKI COM DE SALVADOS LTDA</t>
+          <t>Mosaic Fertilizantes do Brasil Ltda</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
@@ -8847,7 +8847,7 @@
       <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr">
         <is>
-          <t>BOM FUTURO AGRICOLA LTDA</t>
+          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
@@ -8939,7 +8939,7 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>43331955191</t>
+          <t>05089654000157</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -8950,7 +8950,7 @@
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr">
         <is>
-          <t>DEISE LAINE ALVES</t>
+          <t>TINDIANA LOGISTICA E TRANSPORTES LTDA</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
@@ -9012,7 +9012,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32960</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -9042,7 +9042,7 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>43331955191</t>
+          <t>05089654000157</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -9053,7 +9053,7 @@
       <c r="Q84" t="inlineStr"/>
       <c r="R84" t="inlineStr">
         <is>
-          <t>DEISE LAINE ALVES</t>
+          <t>TINDIANA LOGISTICA E TRANSPORTES LTDA</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
@@ -9156,7 +9156,7 @@
       <c r="Q85" t="inlineStr"/>
       <c r="R85" t="inlineStr">
         <is>
-          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
+          <t>RODOFROTA TRANSPORTES RODOVIARIOS E LOGISTICA LTDA</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
@@ -9198,7 +9198,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Mosaic Fertilizantes P&amp;K Ltda</t>
+          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -9218,7 +9218,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>48</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -9243,7 +9243,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>33931486001455</t>
+          <t>29406625000130</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
@@ -9259,7 +9259,7 @@
       <c r="Q86" t="inlineStr"/>
       <c r="R86" t="inlineStr">
         <is>
-          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
+          <t>TRANSPORTES RODOVIARIOS VALE DO PIQUIRI LTDA</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
@@ -9321,7 +9321,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>48</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -9346,12 +9346,12 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
+          <t>29406625000130</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
           <t>33931486001455</t>
-        </is>
-      </c>
-      <c r="O87" t="inlineStr">
-        <is>
-          <t>92660604012865</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -9362,7 +9362,7 @@
       <c r="Q87" t="inlineStr"/>
       <c r="R87" t="inlineStr">
         <is>
-          <t>YARA BRASIL FERTILIZANTES SA</t>
+          <t>RODOFROTA TRANSPORTES RODOVIARIOS E LOGISTICA LTDA</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
@@ -9424,7 +9424,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>47</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -9449,12 +9449,12 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
+          <t>29406625000130</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
           <t>33931486001455</t>
-        </is>
-      </c>
-      <c r="O88" t="inlineStr">
-        <is>
-          <t>92660604012865</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -9465,7 +9465,7 @@
       <c r="Q88" t="inlineStr"/>
       <c r="R88" t="inlineStr">
         <is>
-          <t>YARA BRASIL FERTILIZANTES SA</t>
+          <t>RODOFROTA TRANSPORTES RODOVIARIOS E LOGISTICA LTDA</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
@@ -9507,7 +9507,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Mosaic Fertilizantes P&amp;K Ltda</t>
+          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -9527,7 +9527,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>48</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -9552,7 +9552,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>33931486001455</t>
+          <t>29406625000130</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
@@ -9568,7 +9568,7 @@
       <c r="Q89" t="inlineStr"/>
       <c r="R89" t="inlineStr">
         <is>
-          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA</t>
+          <t>TRANSPORTES RODOVIARIOS VALE DO PIQUIRI LTDA</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
@@ -9630,7 +9630,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>47060</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -9671,7 +9671,7 @@
       <c r="Q90" t="inlineStr"/>
       <c r="R90" t="inlineStr">
         <is>
-          <t>CTO 1 AGROPECUARIA S.A.</t>
+          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
@@ -9733,7 +9733,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>47560</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -9774,7 +9774,7 @@
       <c r="Q91" t="inlineStr"/>
       <c r="R91" t="inlineStr">
         <is>
-          <t>CTO 1 AGROPECUARIA S.A.</t>
+          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
@@ -9836,7 +9836,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>47620</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -9877,7 +9877,7 @@
       <c r="Q92" t="inlineStr"/>
       <c r="R92" t="inlineStr">
         <is>
-          <t>CTO 1 AGROPECUARIA S.A.</t>
+          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
@@ -9939,7 +9939,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>47040</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -9980,7 +9980,7 @@
       <c r="Q93" t="inlineStr"/>
       <c r="R93" t="inlineStr">
         <is>
-          <t>CTO 1 AGROPECUARIA S.A.</t>
+          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
@@ -10022,7 +10022,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Mosaic Fertilizantes P&amp;K Ltda</t>
+          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -10042,7 +10042,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -10067,7 +10067,7 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>33931486001455</t>
+          <t>29406625000130</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
@@ -10083,7 +10083,7 @@
       <c r="Q94" t="inlineStr"/>
       <c r="R94" t="inlineStr">
         <is>
-          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
+          <t>RODOFROTA TRANSPORTES RODOVIARIOS E LOGISTICA LTDA</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
@@ -10145,7 +10145,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>47700</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -10186,7 +10186,7 @@
       <c r="Q95" t="inlineStr"/>
       <c r="R95" t="inlineStr">
         <is>
-          <t>CTO 1 AGROPECUARIA S.A.</t>
+          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>36660</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -10289,7 +10289,7 @@
       <c r="Q96" t="inlineStr"/>
       <c r="R96" t="inlineStr">
         <is>
-          <t>CTO 1 AGROPECUARIA S.A.</t>
+          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
         </is>
       </c>
       <c r="S96" t="inlineStr">
@@ -10331,7 +10331,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Mosaic Fertilizantes P&amp;K Ltda</t>
+          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -10351,7 +10351,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>47</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>33931486001455</t>
+          <t>29406625000130</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
@@ -10392,7 +10392,7 @@
       <c r="Q97" t="inlineStr"/>
       <c r="R97" t="inlineStr">
         <is>
-          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
+          <t>BUDEL TRANSPORTES LTDA</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
@@ -10454,7 +10454,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>35670</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -10495,7 +10495,7 @@
       <c r="Q98" t="inlineStr"/>
       <c r="R98" t="inlineStr">
         <is>
-          <t>FOSPAR S/A</t>
+          <t>BUDEL TRANSPORTES LTDA</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
@@ -10598,7 +10598,7 @@
       <c r="Q99" t="inlineStr"/>
       <c r="R99" t="inlineStr">
         <is>
-          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
+          <t>TRANSPORTES RODOVIARIOS VALE DO PIQUIRI LTDA</t>
         </is>
       </c>
       <c r="S99" t="inlineStr">
@@ -10701,7 +10701,7 @@
       <c r="Q100" t="inlineStr"/>
       <c r="R100" t="inlineStr">
         <is>
-          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
+          <t>TRANSVAL TRANSPORTADORA VALMIR LTDA</t>
         </is>
       </c>
       <c r="S100" t="inlineStr">
@@ -10804,7 +10804,7 @@
       <c r="Q101" t="inlineStr"/>
       <c r="R101" t="inlineStr">
         <is>
-          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
+          <t>TRANSPORTES RODOVIARIOS VALE DO PIQUIRI LTDA</t>
         </is>
       </c>
       <c r="S101" t="inlineStr">
@@ -10907,7 +10907,7 @@
       <c r="Q102" t="inlineStr"/>
       <c r="R102" t="inlineStr">
         <is>
-          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
+          <t>RODO M LOGISTICA E SERVICOS LTDA</t>
         </is>
       </c>
       <c r="S102" t="inlineStr">
@@ -11010,7 +11010,7 @@
       <c r="Q103" t="inlineStr"/>
       <c r="R103" t="inlineStr">
         <is>
-          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
+          <t>TRANSPORTES RODOVIARIOS VALE DO PIQUIRI LTDA</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
@@ -11113,7 +11113,7 @@
       <c r="Q104" t="inlineStr"/>
       <c r="R104" t="inlineStr">
         <is>
-          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
+          <t>TRANSPORTES RODOVIARIOS VALE DO PIQUIRI LTDA</t>
         </is>
       </c>
       <c r="S104" t="inlineStr">
@@ -11216,7 +11216,7 @@
       <c r="Q105" t="inlineStr"/>
       <c r="R105" t="inlineStr">
         <is>
-          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
+          <t>TRANSVAL TRANSPORTADORA VALMIR LTDA</t>
         </is>
       </c>
       <c r="S105" t="inlineStr">
@@ -11319,7 +11319,7 @@
       <c r="Q106" t="inlineStr"/>
       <c r="R106" t="inlineStr">
         <is>
-          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
+          <t>RODO M LOGISTICA E SERVICOS LTDA</t>
         </is>
       </c>
       <c r="S106" t="inlineStr">
@@ -11422,7 +11422,7 @@
       <c r="Q107" t="inlineStr"/>
       <c r="R107" t="inlineStr">
         <is>
-          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
+          <t>BUDEL TRANSPORTES LTDA</t>
         </is>
       </c>
       <c r="S107" t="inlineStr">
@@ -11525,7 +11525,7 @@
       <c r="Q108" t="inlineStr"/>
       <c r="R108" t="inlineStr">
         <is>
-          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
+          <t>BUDEL TRANSPORTES LTDA</t>
         </is>
       </c>
       <c r="S108" t="inlineStr">
@@ -11587,7 +11587,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22390</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -11628,7 +11628,7 @@
       <c r="Q109" t="inlineStr"/>
       <c r="R109" t="inlineStr">
         <is>
-          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA I</t>
+          <t>BRONOVSKI COMERCIO DE SALVADOS LTDA</t>
         </is>
       </c>
       <c r="S109" t="inlineStr">
@@ -11731,7 +11731,7 @@
       <c r="Q110" t="inlineStr"/>
       <c r="R110" t="inlineStr">
         <is>
-          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
+          <t>BUDEL TRANSPORTES LTDA</t>
         </is>
       </c>
       <c r="S110" t="inlineStr">
@@ -11834,7 +11834,7 @@
       <c r="Q111" t="inlineStr"/>
       <c r="R111" t="inlineStr">
         <is>
-          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
+          <t>FERTRAN TRANSPORTES LTDA</t>
         </is>
       </c>
       <c r="S111" t="inlineStr">
@@ -11896,7 +11896,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22390</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -11937,7 +11937,7 @@
       <c r="Q112" t="inlineStr"/>
       <c r="R112" t="inlineStr">
         <is>
-          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA I</t>
+          <t>BRONOVSKI COMERCIO DE SALVADOS LTDA</t>
         </is>
       </c>
       <c r="S112" t="inlineStr">
@@ -11999,7 +11999,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>48680</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -12040,7 +12040,7 @@
       <c r="Q113" t="inlineStr"/>
       <c r="R113" t="inlineStr">
         <is>
-          <t>BOM FUTURO AGRICOLA LTDA</t>
+          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
         </is>
       </c>
       <c r="S113" t="inlineStr">
@@ -12102,7 +12102,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>51220</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -12143,7 +12143,7 @@
       <c r="Q114" t="inlineStr"/>
       <c r="R114" t="inlineStr">
         <is>
-          <t>BOM FUTURO AGRICOLA LTDA</t>
+          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
         </is>
       </c>
       <c r="S114" t="inlineStr">
@@ -12205,7 +12205,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>48980</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -12246,7 +12246,7 @@
       <c r="Q115" t="inlineStr"/>
       <c r="R115" t="inlineStr">
         <is>
-          <t>BOM FUTURO AGRICOLA LTDA</t>
+          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
         </is>
       </c>
       <c r="S115" t="inlineStr">
@@ -12349,7 +12349,7 @@
       <c r="Q116" t="inlineStr"/>
       <c r="R116" t="inlineStr">
         <is>
-          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
+          <t>G10 TRANSPORTES S A</t>
         </is>
       </c>
       <c r="S116" t="inlineStr">
@@ -12452,7 +12452,7 @@
       <c r="Q117" t="inlineStr"/>
       <c r="R117" t="inlineStr">
         <is>
-          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
+          <t>G10 TRANSPORTES S A</t>
         </is>
       </c>
       <c r="S117" t="inlineStr">
@@ -12555,7 +12555,7 @@
       <c r="Q118" t="inlineStr"/>
       <c r="R118" t="inlineStr">
         <is>
-          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
+          <t>BUDEL TRANSPORTES LTDA</t>
         </is>
       </c>
       <c r="S118" t="inlineStr">
@@ -12617,7 +12617,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18000</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -12658,7 +12658,7 @@
       <c r="Q119" t="inlineStr"/>
       <c r="R119" t="inlineStr">
         <is>
-          <t>COONAGRO COOPERATIVA NACIONAL</t>
+          <t>LOGIC TRANSPORTES EIRELI</t>
         </is>
       </c>
       <c r="S119" t="inlineStr">
@@ -12720,7 +12720,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17800</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -12761,7 +12761,7 @@
       <c r="Q120" t="inlineStr"/>
       <c r="R120" t="inlineStr">
         <is>
-          <t>COONAGRO COOPERATIVA NACIONAL</t>
+          <t>LOGIC TRANSPORTES EIRELI</t>
         </is>
       </c>
       <c r="S120" t="inlineStr">
@@ -12823,7 +12823,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28540</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -12864,7 +12864,7 @@
       <c r="Q121" t="inlineStr"/>
       <c r="R121" t="inlineStr">
         <is>
-          <t>BRONOVSKI COM DE SALVADOS LTDA</t>
+          <t>Mosaic Fertilizantes do Brasil Ltda</t>
         </is>
       </c>
       <c r="S121" t="inlineStr">
@@ -12926,7 +12926,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17800</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -12967,7 +12967,7 @@
       <c r="Q122" t="inlineStr"/>
       <c r="R122" t="inlineStr">
         <is>
-          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA I</t>
+          <t>LOGIC TRANSPORTES EIRELI</t>
         </is>
       </c>
       <c r="S122" t="inlineStr">
@@ -13029,7 +13029,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>48980</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -13070,7 +13070,7 @@
       <c r="Q123" t="inlineStr"/>
       <c r="R123" t="inlineStr">
         <is>
-          <t>BOM FUTURO AGRICOLA LTDA</t>
+          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
         </is>
       </c>
       <c r="S123" t="inlineStr">
@@ -13132,7 +13132,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>49140</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -13173,7 +13173,7 @@
       <c r="Q124" t="inlineStr"/>
       <c r="R124" t="inlineStr">
         <is>
-          <t>BOM FUTURO AGRICOLA LTDA</t>
+          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
         </is>
       </c>
       <c r="S124" t="inlineStr">
@@ -13235,7 +13235,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>49420</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -13276,7 +13276,7 @@
       <c r="Q125" t="inlineStr"/>
       <c r="R125" t="inlineStr">
         <is>
-          <t>BOM FUTURO AGRICOLA LTDA</t>
+          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
         </is>
       </c>
       <c r="S125" t="inlineStr">
@@ -13338,7 +13338,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>49180</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -13379,7 +13379,7 @@
       <c r="Q126" t="inlineStr"/>
       <c r="R126" t="inlineStr">
         <is>
-          <t>BOM FUTURO AGRICOLA LTDA</t>
+          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
         </is>
       </c>
       <c r="S126" t="inlineStr">
@@ -13441,7 +13441,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>47540</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -13482,7 +13482,7 @@
       <c r="Q127" t="inlineStr"/>
       <c r="R127" t="inlineStr">
         <is>
-          <t>BOM FUTURO AGRICOLA LTDA</t>
+          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
         </is>
       </c>
       <c r="S127" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>49620</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -13585,7 +13585,7 @@
       <c r="Q128" t="inlineStr"/>
       <c r="R128" t="inlineStr">
         <is>
-          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA I</t>
+          <t>GRANLIDER TRANSPORTES E AGENCIAMENTOS DE CARGAS LTDA</t>
         </is>
       </c>
       <c r="S128" t="inlineStr">
@@ -13647,7 +13647,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>48360</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -13688,7 +13688,7 @@
       <c r="Q129" t="inlineStr"/>
       <c r="R129" t="inlineStr">
         <is>
-          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA I</t>
+          <t>GRANLIDER TRANSPORTES E AGENCIAMENTOS DE CARGAS LTDA</t>
         </is>
       </c>
       <c r="S129" t="inlineStr">
@@ -13791,7 +13791,7 @@
       <c r="Q130" t="inlineStr"/>
       <c r="R130" t="inlineStr">
         <is>
-          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
+          <t>LONTANO TRANSPORTES LTDA</t>
         </is>
       </c>
       <c r="S130" t="inlineStr">
@@ -13853,27 +13853,27 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>47450</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CONCLUÍDO</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>05/05/2026 10:10:20</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>TEIXEIRA, JOAO - Paranagua 2, PR</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5785</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -13883,28 +13883,28 @@
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>61156501008050</t>
+          <t>10425282003300</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ajuste de caracteres na OV.”</t>
         </is>
       </c>
       <c r="Q131" t="inlineStr"/>
       <c r="R131" t="inlineStr">
         <is>
-          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA I</t>
+          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
         </is>
       </c>
       <c r="S131" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
         </is>
       </c>
       <c r="T131" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>6106</t>
         </is>
       </c>
       <c r="U131" t="inlineStr">
@@ -13956,7 +13956,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>49620</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -13997,7 +13997,7 @@
       <c r="Q132" t="inlineStr"/>
       <c r="R132" t="inlineStr">
         <is>
-          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA I</t>
+          <t>GRANLIDER TRANSPORTES E AGENCIAMENTOS DE CARGAS LTDA</t>
         </is>
       </c>
       <c r="S132" t="inlineStr">
@@ -14059,7 +14059,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>47450</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -14100,7 +14100,7 @@
       <c r="Q133" t="inlineStr"/>
       <c r="R133" t="inlineStr">
         <is>
-          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA I</t>
+          <t>GRANLIDER TRANSPORTES E AGENCIAMENTOS DE CARGAS LTDA</t>
         </is>
       </c>
       <c r="S133" t="inlineStr">
@@ -14162,27 +14162,27 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>47100</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>CONCLUÍDO</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>05/05/2026 10:23:03</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>TEIXEIRA, JOAO - Paranagua 2, PR</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5786</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -14192,28 +14192,28 @@
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>61156501008050</t>
+          <t>10425282003300</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ajuste de caracteres na OV.”</t>
         </is>
       </c>
       <c r="Q134" t="inlineStr"/>
       <c r="R134" t="inlineStr">
         <is>
-          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA I</t>
+          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
         </is>
       </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
         </is>
       </c>
       <c r="T134" t="inlineStr">
         <is>
-          <t>N/D</t>
+          <t>6106</t>
         </is>
       </c>
       <c r="U134" t="inlineStr">
@@ -14265,7 +14265,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>37760</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -14306,7 +14306,7 @@
       <c r="Q135" t="inlineStr"/>
       <c r="R135" t="inlineStr">
         <is>
-          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA I</t>
+          <t>GRANLIDER TRANSPORTES E AGENCIAMENTOS DE CARGAS LTDA</t>
         </is>
       </c>
       <c r="S135" t="inlineStr">
@@ -14368,7 +14368,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>49460</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -14409,7 +14409,7 @@
       <c r="Q136" t="inlineStr"/>
       <c r="R136" t="inlineStr">
         <is>
-          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA I</t>
+          <t>GRANLIDER TRANSPORTES E AGENCIAMENTOS DE CARGAS LTDA</t>
         </is>
       </c>
       <c r="S136" t="inlineStr">
@@ -14425,6 +14425,212 @@
       <c r="U136" t="inlineStr">
         <is>
           <t>NÃO (Assistente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>TROCA DE NOTA - MOSAIC UBERABA MAP - PLACA: spn2g40</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>EXPEDIÇÂO MULTITRANS AZ3</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>05/05/2026 10:13:09</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q137" t="inlineStr"/>
+      <c r="R137" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>NÃO (Armazém)</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>TROCA DE NOTA - MOSAIC UBERABA MAP - PLACA: spn2g40</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>EXPEDIÇÂO MULTITRANS AZ3</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>05/05/2026 10:13:22</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>CONCLUÍDO</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>05/05/2026 10:33:08</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>TEIXEIRA, JOAO - Paranagua 2, PR</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>510147</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>01201578003275</t>
+        </is>
+      </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q138" t="inlineStr"/>
+      <c r="R138" t="inlineStr">
+        <is>
+          <t>G10 TRANSPORTES S A</t>
+        </is>
+      </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>G10 TRANSPORTES S A</t>
+        </is>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>5905</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>NÃO (Armazém)</t>
         </is>
       </c>
     </row>

--- a/Final Report/Relatorio_Controle_Trocas.xlsx
+++ b/Final Report/Relatorio_Controle_Trocas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U138"/>
+  <dimension ref="A1:U144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -752,7 +752,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MOSAIC FERTILIZANTES BRASIL LTDA</t>
+          <t>ICL America do Sul S.A</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>00910509000171</t>
+          <t>60398138000546</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -813,7 +813,7 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
-          <t>RODOFROTA TRANSP RODOVIARIOS LOGIST LTDA</t>
+          <t>MOSAIC FERTILIZANTES BRASIL LTDA</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MOSAIC FERTILIZANTES BRASIL LTDA</t>
+          <t>ICL America do Sul S.A</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>00910509000171</t>
+          <t>60398138000546</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -916,7 +916,7 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
-          <t>RODOFROTA TRANSP RODOVIARIOS LOGIST LTDA</t>
+          <t>MOSAIC FERTILIZANTES BRASIL LTDA</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1431,7 +1431,7 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
-          <t>TRANS CINCO TRANSPORTES RODOVIARIOS</t>
+          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1534,7 +1534,7 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
-          <t>TRANS CINCO TRANSPORTES RODOVIARIOS</t>
+          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1637,7 +1637,7 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
-          <t>TRANS CINCO TRANSPORTES RODOVIARIOS</t>
+          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1740,7 +1740,7 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
-          <t>TINDIANA LOGISTICA E TRANSPORTE LTDA</t>
+          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA II</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1843,7 +1843,7 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
-          <t>TINDIANA LOGISTICA E TRANSPORTE LTDA</t>
+          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA II</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1946,7 +1946,7 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
         <is>
-          <t>GRANLIDER TRANSPORTES E AGENCIAMENTOS DE CARGAS LTDA</t>
+          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA I</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -2049,7 +2049,7 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
         <is>
-          <t>GRANLIDER TRANSPORTES E AGENCIAMENTOS DE CARGAS LTDA</t>
+          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA I</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2152,7 +2152,7 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
         <is>
-          <t>GRANLIDER TRANSPORTES E AGENCIAMENTOS DE CARGAS LTDA</t>
+          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA I</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2255,7 +2255,7 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
         <is>
-          <t>TINDIANA LOGISTICA E TRANSPORTE LTDA</t>
+          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA II</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2358,7 +2358,7 @@
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
         <is>
-          <t>LOGIC TRANSPORTES EIRELI</t>
+          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA I</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2461,7 +2461,7 @@
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
         <is>
-          <t>LOGIC TRANSPORTES EIRELI</t>
+          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA I</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2564,7 +2564,7 @@
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
         <is>
-          <t>GRANLIDER TRANSPORTES E AGENCIAMENTOS DE CARGAS LTDA</t>
+          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA I</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2667,7 +2667,7 @@
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
         <is>
-          <t>TRANSCORONEL TRANSPORTES E LOGISTICA LTDA</t>
+          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA I</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2873,7 +2873,7 @@
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
         <is>
-          <t>TRANS-CINCO TRANSPORTES RODOVIARIOS LTDAEPP</t>
+          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA I</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -2976,7 +2976,7 @@
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
         <is>
-          <t>GRANLIDER TRANSPORTES E AGENCIAMENTOS DE CARGAS LTDA</t>
+          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA I</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3079,7 +3079,7 @@
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
         <is>
-          <t>TINDIANA LOGISTICA E TRANSPORTE LTDA</t>
+          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA II</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3182,7 +3182,7 @@
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
         <is>
-          <t>TRANSCORONEL TRANSPORTES E LOGISTICA LTDA</t>
+          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA I</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3388,7 +3388,7 @@
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
         <is>
-          <t>LOGIC TRANSPORTES EIRELI</t>
+          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA I</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3491,7 +3491,7 @@
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
         <is>
-          <t>LOGIC TRANSPORTES EIRELI</t>
+          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA I</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3594,7 +3594,7 @@
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
         <is>
-          <t>GRANLIDER TRANSPORTES E AGENCIAMENTOS DE CARGAS LTDA</t>
+          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA I</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3697,7 +3697,7 @@
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
         <is>
-          <t>GRANLIDER TRANSPORTES E AGENCIAMENTOS DE CARGAS LTDA</t>
+          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA I</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3800,7 +3800,7 @@
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
         <is>
-          <t>LOGIC TRANSPORTES EIRELI</t>
+          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA I</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -3903,7 +3903,7 @@
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
         <is>
-          <t>TINDIANA LOGISTICA E TRANSPORTE LTDA</t>
+          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA II</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -4006,7 +4006,7 @@
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
         <is>
-          <t>LOGIC TRANSPORTES EIRELI</t>
+          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA I</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4212,7 +4212,7 @@
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr">
         <is>
-          <t>TRANSPORTADORA BOA VIAGEM LTDA</t>
+          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4315,7 +4315,7 @@
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr">
         <is>
-          <t>TRANSPORTADORA BOA VIAGEM LTDA</t>
+          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4418,7 +4418,7 @@
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr">
         <is>
-          <t>RODOFROTA TRANSPORTES RODOVIARIOS E LOGISTICA LTDA</t>
+          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4521,7 +4521,7 @@
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr">
         <is>
-          <t>G10 TRANSPORTES S A</t>
+          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -4624,7 +4624,7 @@
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr">
         <is>
-          <t>TRANSPORTADORA BOA VIAGEM LTDA</t>
+          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -4727,7 +4727,7 @@
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr">
         <is>
-          <t>TINDIANA LOGISTICA E TRANSPORTE LTDA</t>
+          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA II</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>05089654000157</t>
+          <t>43331955191</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -4830,7 +4830,7 @@
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr">
         <is>
-          <t>TINDIANA LOGISTICA E TRANSPORTES LTDA</t>
+          <t>DEISE LAINE ALVES</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -4922,7 +4922,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>05089654000157</t>
+          <t>43331955191</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -4933,7 +4933,7 @@
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr">
         <is>
-          <t>TINDIANA LOGISTICA E TRANSPORTES LTDA</t>
+          <t>DEISE LAINE ALVES</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5036,7 +5036,7 @@
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr">
         <is>
-          <t>TRANSVAL TRANSPORTADORA VALMIR LTDA</t>
+          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -5139,7 +5139,7 @@
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr">
         <is>
-          <t>TRANS CINCO TRANSPORTES RODOVIARIOS</t>
+          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -5345,7 +5345,7 @@
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr">
         <is>
-          <t>TINDIANA LOGISTICA E TRANSPORTE LTDA</t>
+          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA II</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -5448,7 +5448,7 @@
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr">
         <is>
-          <t>TRANS-CINCO TRANSP RODOVIARIOS LTDA</t>
+          <t>AUTEM DO BRASIL LTDA</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -5551,7 +5551,7 @@
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr">
         <is>
-          <t>TRANS-CINCO TRANSP RODOVIARIOS LTDA</t>
+          <t>AUTEM DO BRASIL LTDA</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -5654,7 +5654,7 @@
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr">
         <is>
-          <t>Mosaic Fertilizantes do Brasil Ltda</t>
+          <t>BRONOVSKI COM DE SALVADOS LTDA</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -5757,7 +5757,7 @@
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr">
         <is>
-          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
+          <t>CTO 1 AGROPECUARIA S.A.</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -5860,7 +5860,7 @@
       <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr">
         <is>
-          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
+          <t>CTO 1 AGROPECUARIA S.A.</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -5963,7 +5963,7 @@
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr">
         <is>
-          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
+          <t>BOM FUTURO AGRICOLA LTDA</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -6066,7 +6066,7 @@
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr">
         <is>
-          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
+          <t>CTO 1 AGROPECUARIA SA</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -6169,7 +6169,7 @@
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr">
         <is>
-          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
+          <t>CTO 1 AGROPECUARIA SA</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -6272,7 +6272,7 @@
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr">
         <is>
-          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
+          <t>CTO 1 AGROPECUARIA SA</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -6375,7 +6375,7 @@
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr">
         <is>
-          <t>FERTRAN TRANSPORTES LTDA</t>
+          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -6478,7 +6478,7 @@
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr">
         <is>
-          <t>AGROLOG TRANSPORT CARGAS GERAL LTDA</t>
+          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -6581,7 +6581,7 @@
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr">
         <is>
-          <t>BUDEL TRANSPORTES LTDA</t>
+          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -6684,7 +6684,7 @@
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr">
         <is>
-          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
+          <t>CTO 1 AGROPECUARIA S.A.</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
@@ -6787,7 +6787,7 @@
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr">
         <is>
-          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
+          <t>CTO 1 AGROPECUARIA S.A.</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
@@ -6890,7 +6890,7 @@
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr">
         <is>
-          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
+          <t>CTO 1 AGROPECUARIA S.A.</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -6993,7 +6993,7 @@
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr">
         <is>
-          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
+          <t>BOM FUTURO AGRICOLA LTDA</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
@@ -7096,7 +7096,7 @@
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr">
         <is>
-          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
+          <t>BOM FUTURO AGRICOLA LTDA</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
@@ -7153,7 +7153,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>25000</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -7199,7 +7199,7 @@
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr">
         <is>
-          <t>DIVONSIR PRIEVE 02917886960</t>
+          <t>COONAGRO COOPERATIVA NACIONAL</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
@@ -7302,7 +7302,7 @@
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr">
         <is>
-          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
+          <t>CTO 1 AGROPECUARIA SA</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
@@ -7405,7 +7405,7 @@
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr">
         <is>
-          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
+          <t>CTO 1 AGROPECUARIA SA</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -7508,7 +7508,7 @@
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr">
         <is>
-          <t>47059545 DIVONSIR PRIEVE</t>
+          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA I</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
@@ -7611,7 +7611,7 @@
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr">
         <is>
-          <t>GRANLIDER TRANSPORTES E AGENCIAMENTOS DE CARGAS LTDA</t>
+          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA I</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
@@ -7714,7 +7714,7 @@
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr">
         <is>
-          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
+          <t>CTO 1 AGROPECUARIA S.A.</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
@@ -7817,7 +7817,7 @@
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr">
         <is>
-          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
+          <t>CTO 1 AGROPECUARIA S.A.</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
@@ -7920,7 +7920,7 @@
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr">
         <is>
-          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
+          <t>CTO 1 AGROPECUARIA S.A.</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
@@ -8023,7 +8023,7 @@
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr">
         <is>
-          <t>RODOFROTA TRANSPORTES RODOVIARIOS E LOGISTICA LTDA</t>
+          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
@@ -8126,7 +8126,7 @@
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr">
         <is>
-          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
+          <t>CTO 1 AGROPECUARIA S.A.</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
@@ -8229,7 +8229,7 @@
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr">
         <is>
-          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
+          <t>CTO 1 AGROPECUARIA SA</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
@@ -8332,7 +8332,7 @@
       <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr">
         <is>
-          <t>RODOPAR TRANSPORTES RODOVIARIOS LTD RODOPAR TRANSPORTES RODO</t>
+          <t>BOM FUTURO AGRICOLA LTDA</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
@@ -8435,7 +8435,7 @@
       <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr">
         <is>
-          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
+          <t>CTO 1 AGROPECUARIA S.A.</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
@@ -8538,7 +8538,7 @@
       <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr">
         <is>
-          <t>RODO M LOGISTICA E SERVICOS LTDA</t>
+          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
@@ -8641,7 +8641,7 @@
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr">
         <is>
-          <t>TRANSVAL TRANSPORTADORA VALMIR LTDA</t>
+          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
@@ -8744,7 +8744,7 @@
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr">
         <is>
-          <t>Mosaic Fertilizantes do Brasil Ltda</t>
+          <t>BRONOVSKI COM DE SALVADOS LTDA</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
@@ -8847,7 +8847,7 @@
       <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr">
         <is>
-          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
+          <t>BOM FUTURO AGRICOLA LTDA</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
@@ -8939,7 +8939,7 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>05089654000157</t>
+          <t>43331955191</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -8950,7 +8950,7 @@
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr">
         <is>
-          <t>TINDIANA LOGISTICA E TRANSPORTES LTDA</t>
+          <t>DEISE LAINE ALVES</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
@@ -9042,7 +9042,7 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>05089654000157</t>
+          <t>43331955191</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -9053,7 +9053,7 @@
       <c r="Q84" t="inlineStr"/>
       <c r="R84" t="inlineStr">
         <is>
-          <t>TINDIANA LOGISTICA E TRANSPORTES LTDA</t>
+          <t>DEISE LAINE ALVES</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
@@ -9156,7 +9156,7 @@
       <c r="Q85" t="inlineStr"/>
       <c r="R85" t="inlineStr">
         <is>
-          <t>RODOFROTA TRANSPORTES RODOVIARIOS E LOGISTICA LTDA</t>
+          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
@@ -9198,7 +9198,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA</t>
+          <t>Mosaic Fertilizantes P&amp;K Ltda</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -9243,7 +9243,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>29406625000130</t>
+          <t>33931486001455</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
@@ -9259,7 +9259,7 @@
       <c r="Q86" t="inlineStr"/>
       <c r="R86" t="inlineStr">
         <is>
-          <t>TRANSPORTES RODOVIARIOS VALE DO PIQUIRI LTDA</t>
+          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
@@ -9346,12 +9346,12 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>29406625000130</t>
+          <t>33931486001455</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>33931486001455</t>
+          <t>92660604012865</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -9362,7 +9362,7 @@
       <c r="Q87" t="inlineStr"/>
       <c r="R87" t="inlineStr">
         <is>
-          <t>RODOFROTA TRANSPORTES RODOVIARIOS E LOGISTICA LTDA</t>
+          <t>YARA BRASIL FERTILIZANTES SA</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
@@ -9449,12 +9449,12 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>29406625000130</t>
+          <t>33931486001455</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>33931486001455</t>
+          <t>92660604012865</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -9465,7 +9465,7 @@
       <c r="Q88" t="inlineStr"/>
       <c r="R88" t="inlineStr">
         <is>
-          <t>RODOFROTA TRANSPORTES RODOVIARIOS E LOGISTICA LTDA</t>
+          <t>YARA BRASIL FERTILIZANTES SA</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
@@ -9507,7 +9507,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA</t>
+          <t>Mosaic Fertilizantes P&amp;K Ltda</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -9552,7 +9552,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>29406625000130</t>
+          <t>33931486001455</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
@@ -9568,7 +9568,7 @@
       <c r="Q89" t="inlineStr"/>
       <c r="R89" t="inlineStr">
         <is>
-          <t>TRANSPORTES RODOVIARIOS VALE DO PIQUIRI LTDA</t>
+          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
@@ -9671,7 +9671,7 @@
       <c r="Q90" t="inlineStr"/>
       <c r="R90" t="inlineStr">
         <is>
-          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
+          <t>CTO 1 AGROPECUARIA S.A.</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
@@ -9774,7 +9774,7 @@
       <c r="Q91" t="inlineStr"/>
       <c r="R91" t="inlineStr">
         <is>
-          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
+          <t>CTO 1 AGROPECUARIA S.A.</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
@@ -9877,7 +9877,7 @@
       <c r="Q92" t="inlineStr"/>
       <c r="R92" t="inlineStr">
         <is>
-          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
+          <t>CTO 1 AGROPECUARIA S.A.</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
@@ -9980,7 +9980,7 @@
       <c r="Q93" t="inlineStr"/>
       <c r="R93" t="inlineStr">
         <is>
-          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
+          <t>CTO 1 AGROPECUARIA S.A.</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
@@ -10022,7 +10022,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA</t>
+          <t>Mosaic Fertilizantes P&amp;K Ltda</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -10067,7 +10067,7 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>29406625000130</t>
+          <t>33931486001455</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
@@ -10083,7 +10083,7 @@
       <c r="Q94" t="inlineStr"/>
       <c r="R94" t="inlineStr">
         <is>
-          <t>RODOFROTA TRANSPORTES RODOVIARIOS E LOGISTICA LTDA</t>
+          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
@@ -10186,7 +10186,7 @@
       <c r="Q95" t="inlineStr"/>
       <c r="R95" t="inlineStr">
         <is>
-          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
+          <t>CTO 1 AGROPECUARIA S.A.</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
@@ -10289,7 +10289,7 @@
       <c r="Q96" t="inlineStr"/>
       <c r="R96" t="inlineStr">
         <is>
-          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
+          <t>CTO 1 AGROPECUARIA S.A.</t>
         </is>
       </c>
       <c r="S96" t="inlineStr">
@@ -10331,7 +10331,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA</t>
+          <t>Mosaic Fertilizantes P&amp;K Ltda</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>29406625000130</t>
+          <t>33931486001455</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
@@ -10392,7 +10392,7 @@
       <c r="Q97" t="inlineStr"/>
       <c r="R97" t="inlineStr">
         <is>
-          <t>BUDEL TRANSPORTES LTDA</t>
+          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
@@ -10495,7 +10495,7 @@
       <c r="Q98" t="inlineStr"/>
       <c r="R98" t="inlineStr">
         <is>
-          <t>BUDEL TRANSPORTES LTDA</t>
+          <t>FOSPAR S/A</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
@@ -10598,7 +10598,7 @@
       <c r="Q99" t="inlineStr"/>
       <c r="R99" t="inlineStr">
         <is>
-          <t>TRANSPORTES RODOVIARIOS VALE DO PIQUIRI LTDA</t>
+          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
         </is>
       </c>
       <c r="S99" t="inlineStr">
@@ -10701,7 +10701,7 @@
       <c r="Q100" t="inlineStr"/>
       <c r="R100" t="inlineStr">
         <is>
-          <t>TRANSVAL TRANSPORTADORA VALMIR LTDA</t>
+          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
         </is>
       </c>
       <c r="S100" t="inlineStr">
@@ -10804,7 +10804,7 @@
       <c r="Q101" t="inlineStr"/>
       <c r="R101" t="inlineStr">
         <is>
-          <t>TRANSPORTES RODOVIARIOS VALE DO PIQUIRI LTDA</t>
+          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
         </is>
       </c>
       <c r="S101" t="inlineStr">
@@ -10907,7 +10907,7 @@
       <c r="Q102" t="inlineStr"/>
       <c r="R102" t="inlineStr">
         <is>
-          <t>RODO M LOGISTICA E SERVICOS LTDA</t>
+          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
         </is>
       </c>
       <c r="S102" t="inlineStr">
@@ -11010,7 +11010,7 @@
       <c r="Q103" t="inlineStr"/>
       <c r="R103" t="inlineStr">
         <is>
-          <t>TRANSPORTES RODOVIARIOS VALE DO PIQUIRI LTDA</t>
+          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
@@ -11113,7 +11113,7 @@
       <c r="Q104" t="inlineStr"/>
       <c r="R104" t="inlineStr">
         <is>
-          <t>TRANSPORTES RODOVIARIOS VALE DO PIQUIRI LTDA</t>
+          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
         </is>
       </c>
       <c r="S104" t="inlineStr">
@@ -11216,7 +11216,7 @@
       <c r="Q105" t="inlineStr"/>
       <c r="R105" t="inlineStr">
         <is>
-          <t>TRANSVAL TRANSPORTADORA VALMIR LTDA</t>
+          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
         </is>
       </c>
       <c r="S105" t="inlineStr">
@@ -11319,7 +11319,7 @@
       <c r="Q106" t="inlineStr"/>
       <c r="R106" t="inlineStr">
         <is>
-          <t>RODO M LOGISTICA E SERVICOS LTDA</t>
+          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
         </is>
       </c>
       <c r="S106" t="inlineStr">
@@ -11422,7 +11422,7 @@
       <c r="Q107" t="inlineStr"/>
       <c r="R107" t="inlineStr">
         <is>
-          <t>BUDEL TRANSPORTES LTDA</t>
+          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
         </is>
       </c>
       <c r="S107" t="inlineStr">
@@ -11525,7 +11525,7 @@
       <c r="Q108" t="inlineStr"/>
       <c r="R108" t="inlineStr">
         <is>
-          <t>BUDEL TRANSPORTES LTDA</t>
+          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
         </is>
       </c>
       <c r="S108" t="inlineStr">
@@ -11628,7 +11628,7 @@
       <c r="Q109" t="inlineStr"/>
       <c r="R109" t="inlineStr">
         <is>
-          <t>BRONOVSKI COMERCIO DE SALVADOS LTDA</t>
+          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA I</t>
         </is>
       </c>
       <c r="S109" t="inlineStr">
@@ -11731,7 +11731,7 @@
       <c r="Q110" t="inlineStr"/>
       <c r="R110" t="inlineStr">
         <is>
-          <t>BUDEL TRANSPORTES LTDA</t>
+          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
         </is>
       </c>
       <c r="S110" t="inlineStr">
@@ -11834,7 +11834,7 @@
       <c r="Q111" t="inlineStr"/>
       <c r="R111" t="inlineStr">
         <is>
-          <t>FERTRAN TRANSPORTES LTDA</t>
+          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
         </is>
       </c>
       <c r="S111" t="inlineStr">
@@ -11937,7 +11937,7 @@
       <c r="Q112" t="inlineStr"/>
       <c r="R112" t="inlineStr">
         <is>
-          <t>BRONOVSKI COMERCIO DE SALVADOS LTDA</t>
+          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA I</t>
         </is>
       </c>
       <c r="S112" t="inlineStr">
@@ -12040,7 +12040,7 @@
       <c r="Q113" t="inlineStr"/>
       <c r="R113" t="inlineStr">
         <is>
-          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
+          <t>BOM FUTURO AGRICOLA LTDA</t>
         </is>
       </c>
       <c r="S113" t="inlineStr">
@@ -12143,7 +12143,7 @@
       <c r="Q114" t="inlineStr"/>
       <c r="R114" t="inlineStr">
         <is>
-          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
+          <t>BOM FUTURO AGRICOLA LTDA</t>
         </is>
       </c>
       <c r="S114" t="inlineStr">
@@ -12246,7 +12246,7 @@
       <c r="Q115" t="inlineStr"/>
       <c r="R115" t="inlineStr">
         <is>
-          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
+          <t>BOM FUTURO AGRICOLA LTDA</t>
         </is>
       </c>
       <c r="S115" t="inlineStr">
@@ -12349,7 +12349,7 @@
       <c r="Q116" t="inlineStr"/>
       <c r="R116" t="inlineStr">
         <is>
-          <t>G10 TRANSPORTES S A</t>
+          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
         </is>
       </c>
       <c r="S116" t="inlineStr">
@@ -12452,7 +12452,7 @@
       <c r="Q117" t="inlineStr"/>
       <c r="R117" t="inlineStr">
         <is>
-          <t>G10 TRANSPORTES S A</t>
+          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
         </is>
       </c>
       <c r="S117" t="inlineStr">
@@ -12555,7 +12555,7 @@
       <c r="Q118" t="inlineStr"/>
       <c r="R118" t="inlineStr">
         <is>
-          <t>BUDEL TRANSPORTES LTDA</t>
+          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
         </is>
       </c>
       <c r="S118" t="inlineStr">
@@ -12658,7 +12658,7 @@
       <c r="Q119" t="inlineStr"/>
       <c r="R119" t="inlineStr">
         <is>
-          <t>LOGIC TRANSPORTES EIRELI</t>
+          <t>COONAGRO COOPERATIVA NACIONAL</t>
         </is>
       </c>
       <c r="S119" t="inlineStr">
@@ -12761,7 +12761,7 @@
       <c r="Q120" t="inlineStr"/>
       <c r="R120" t="inlineStr">
         <is>
-          <t>LOGIC TRANSPORTES EIRELI</t>
+          <t>COONAGRO COOPERATIVA NACIONAL</t>
         </is>
       </c>
       <c r="S120" t="inlineStr">
@@ -12864,7 +12864,7 @@
       <c r="Q121" t="inlineStr"/>
       <c r="R121" t="inlineStr">
         <is>
-          <t>Mosaic Fertilizantes do Brasil Ltda</t>
+          <t>BRONOVSKI COM DE SALVADOS LTDA</t>
         </is>
       </c>
       <c r="S121" t="inlineStr">
@@ -12967,7 +12967,7 @@
       <c r="Q122" t="inlineStr"/>
       <c r="R122" t="inlineStr">
         <is>
-          <t>LOGIC TRANSPORTES EIRELI</t>
+          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA I</t>
         </is>
       </c>
       <c r="S122" t="inlineStr">
@@ -13070,7 +13070,7 @@
       <c r="Q123" t="inlineStr"/>
       <c r="R123" t="inlineStr">
         <is>
-          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
+          <t>BOM FUTURO AGRICOLA LTDA</t>
         </is>
       </c>
       <c r="S123" t="inlineStr">
@@ -13173,7 +13173,7 @@
       <c r="Q124" t="inlineStr"/>
       <c r="R124" t="inlineStr">
         <is>
-          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
+          <t>BOM FUTURO AGRICOLA LTDA</t>
         </is>
       </c>
       <c r="S124" t="inlineStr">
@@ -13276,7 +13276,7 @@
       <c r="Q125" t="inlineStr"/>
       <c r="R125" t="inlineStr">
         <is>
-          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
+          <t>BOM FUTURO AGRICOLA LTDA</t>
         </is>
       </c>
       <c r="S125" t="inlineStr">
@@ -13379,7 +13379,7 @@
       <c r="Q126" t="inlineStr"/>
       <c r="R126" t="inlineStr">
         <is>
-          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
+          <t>BOM FUTURO AGRICOLA LTDA</t>
         </is>
       </c>
       <c r="S126" t="inlineStr">
@@ -13482,7 +13482,7 @@
       <c r="Q127" t="inlineStr"/>
       <c r="R127" t="inlineStr">
         <is>
-          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
+          <t>BOM FUTURO AGRICOLA LTDA</t>
         </is>
       </c>
       <c r="S127" t="inlineStr">
@@ -13585,7 +13585,7 @@
       <c r="Q128" t="inlineStr"/>
       <c r="R128" t="inlineStr">
         <is>
-          <t>GRANLIDER TRANSPORTES E AGENCIAMENTOS DE CARGAS LTDA</t>
+          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA I</t>
         </is>
       </c>
       <c r="S128" t="inlineStr">
@@ -13688,7 +13688,7 @@
       <c r="Q129" t="inlineStr"/>
       <c r="R129" t="inlineStr">
         <is>
-          <t>GRANLIDER TRANSPORTES E AGENCIAMENTOS DE CARGAS LTDA</t>
+          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA I</t>
         </is>
       </c>
       <c r="S129" t="inlineStr">
@@ -13791,7 +13791,7 @@
       <c r="Q130" t="inlineStr"/>
       <c r="R130" t="inlineStr">
         <is>
-          <t>LONTANO TRANSPORTES LTDA</t>
+          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
         </is>
       </c>
       <c r="S130" t="inlineStr">
@@ -13894,7 +13894,7 @@
       <c r="Q131" t="inlineStr"/>
       <c r="R131" t="inlineStr">
         <is>
-          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
+          <t>BOM FUTURO AGRICOLA LTDA</t>
         </is>
       </c>
       <c r="S131" t="inlineStr">
@@ -13997,7 +13997,7 @@
       <c r="Q132" t="inlineStr"/>
       <c r="R132" t="inlineStr">
         <is>
-          <t>GRANLIDER TRANSPORTES E AGENCIAMENTOS DE CARGAS LTDA</t>
+          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA I</t>
         </is>
       </c>
       <c r="S132" t="inlineStr">
@@ -14100,7 +14100,7 @@
       <c r="Q133" t="inlineStr"/>
       <c r="R133" t="inlineStr">
         <is>
-          <t>GRANLIDER TRANSPORTES E AGENCIAMENTOS DE CARGAS LTDA</t>
+          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA I</t>
         </is>
       </c>
       <c r="S133" t="inlineStr">
@@ -14203,7 +14203,7 @@
       <c r="Q134" t="inlineStr"/>
       <c r="R134" t="inlineStr">
         <is>
-          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
+          <t>BOM FUTURO AGRICOLA LTDA</t>
         </is>
       </c>
       <c r="S134" t="inlineStr">
@@ -14306,7 +14306,7 @@
       <c r="Q135" t="inlineStr"/>
       <c r="R135" t="inlineStr">
         <is>
-          <t>GRANLIDER TRANSPORTES E AGENCIAMENTOS DE CARGAS LTDA</t>
+          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA I</t>
         </is>
       </c>
       <c r="S135" t="inlineStr">
@@ -14409,7 +14409,7 @@
       <c r="Q136" t="inlineStr"/>
       <c r="R136" t="inlineStr">
         <is>
-          <t>GRANLIDER TRANSPORTES E AGENCIAMENTOS DE CARGAS LTDA</t>
+          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA I</t>
         </is>
       </c>
       <c r="S136" t="inlineStr">
@@ -14615,14 +14615,14 @@
       <c r="Q138" t="inlineStr"/>
       <c r="R138" t="inlineStr">
         <is>
+          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
+        </is>
+      </c>
+      <c r="S138" t="inlineStr">
+        <is>
           <t>G10 TRANSPORTES S A</t>
         </is>
       </c>
-      <c r="S138" t="inlineStr">
-        <is>
-          <t>G10 TRANSPORTES S A</t>
-        </is>
-      </c>
       <c r="T138" t="inlineStr">
         <is>
           <t>5905</t>
@@ -14631,6 +14631,624 @@
       <c r="U138" t="inlineStr">
         <is>
           <t>NÃO (Armazém)</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>TROCA DE NOTA - MOSAIC UBERABA MAP - PLACA: BEY5A21 - DESCARGA DO DIA 13/04 - NOTA DE VENDA 1715370</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>VANESSA COLODEL | ESTOQUE | MULTITRANS</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>05/05/2026 11:29:57</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q139" t="inlineStr"/>
+      <c r="R139" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>NÃO (Armazém)</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>TROCA DE NOTA - MOSAIC X CTO 1 AGROPECUARIA - PLACA: JBP5E25</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>EXPEDIÇÂO MULTITRANS AZ3</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>05/05/2026 11:42:13</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>300199</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>MULTITRANS TRANSP.ARMAZENS GERAIS LTDA - PR</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>KCL 60,5% - CLORETO DE POTASSIO 60,5%, SOL H2O GRANULADO</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>5907</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>49060</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>49060</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>CONCLUÍDO</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>05/05/2026 11:52:33</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>TEIXEIRA, JOAO - Paranagua 2, PR</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>5787</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>01201578003275</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>10597657000301</t>
+        </is>
+      </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q140" t="inlineStr"/>
+      <c r="R140" t="inlineStr">
+        <is>
+          <t>CTO 1 AGROPECUARIA S.A.</t>
+        </is>
+      </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
+        </is>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>6106</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>TROCA DE NOTA - MOSAIC X BOM FUTURO AGRICOLA - PLACA: UAW4F31</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>EXPEDIÇÂO MULTITRANS AZ3</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>05/05/2026 12:12:08</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>300204</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>MULTITRANS TRANSP.ARMAZENS GERAIS LTDA - PR</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>KCL 60,5% - CLORETO DE POTASSIO 60,5%, SOL H2O GRANULADO</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>5907</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>49280</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>49280</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>CONCLUÍDO</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>05/05/2026 12:25:16</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>TEIXEIRA, JOAO - Paranagua 2, PR</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>5788</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>01201578003275</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>10425282003733</t>
+        </is>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q141" t="inlineStr"/>
+      <c r="R141" t="inlineStr">
+        <is>
+          <t>BOM FUTURO AGRICOLA LTDA</t>
+        </is>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
+        </is>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>6106</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>TROCA DE NOTA - MOSAIC X BOM FUTURO AGRICOLA - PLACA: SEY2H93</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>EXPEDIÇÂO MULTITRANS AZ3</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>05/05/2026 12:40:20</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>300207</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>MULTITRANS TRANSP.ARMAZENS GERAIS LTDA - PR</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>KCL 60,5% - CLORETO DE POTASSIO 60,5%, SOL H2O GRANULADO</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>5907</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>49480</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>49480</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>CONCLUÍDO</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>05/05/2026 13:48:45</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>TEIXEIRA, JOAO - Paranagua 2, PR</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>5789</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>01201578003275</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>10425282003733</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q142" t="inlineStr"/>
+      <c r="R142" t="inlineStr">
+        <is>
+          <t>BOM FUTURO AGRICOLA LTDA</t>
+        </is>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
+        </is>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>6106</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>TROCA DE NOTA PLACA: mbk-4e26 MOSAIC X COONAGRO</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>EXPEDIÇÃO | MULTITRANS PARANAGUA</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>05/05/2026 14:05:20</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>690974</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>MULTITRANS TRANSP.ARMAZENS GERAIS LTDA - PR</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>EMB.TRANC.VALV.NITROG.LAMINADA</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>5907</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>CONCLUÍDO</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>05/05/2026 14:19:00</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>TEIXEIRA, JOAO - Paranagua 2, PR</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>5790</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>01201578000250</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>84828003000370</t>
+        </is>
+      </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q143" t="inlineStr"/>
+      <c r="R143" t="inlineStr">
+        <is>
+          <t>COONAGRO COOPERATIVA NACIONAL</t>
+        </is>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>DIVONSIR PRIEVE 02917886960</t>
+        </is>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>5901</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>TROCA DE NOTA - MOSAIC X BOM FUTURO AGRICOLA - PLACA: AZE-0E60</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>EXPEDIÇÂO MULTITRANS AZ3</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>05/05/2026 15:45:04</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>300217</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>MULTITRANS TRANSP.ARMAZENS GERAIS LTDA - PR</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>KCL 60,5% - CLORETO DE POTASSIO 60,5%, SOL H2O GRANULADO</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>5907</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>49600</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>49600</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>CONCLUÍDO</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>05/05/2026 15:54:36</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>TEIXEIRA, JOAO - Paranagua 2, PR</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>5792</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>01201578003275</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>10425282003733</t>
+        </is>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q144" t="inlineStr"/>
+      <c r="R144" t="inlineStr">
+        <is>
+          <t>BOM FUTURO AGRICOLA LTDA</t>
+        </is>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>GRANLIDER TRANSP E AGENC DE CARGAS LTDA</t>
+        </is>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>6106</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>SIM</t>
         </is>
       </c>
     </row>

--- a/Final Report/Relatorio_Controle_Trocas.xlsx
+++ b/Final Report/Relatorio_Controle_Trocas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U128"/>
+  <dimension ref="A1:U165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13599,6 +13599,3817 @@
         </is>
       </c>
       <c r="U128" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>TROCA DE NOTA - MOSAIC UBERABA MAP - PLACA: FVU1A51</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>EXPEDIÇÂO MULTITRANS AZ3</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>06/05/2026 14:15:36</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>CONCLUÍDO</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>06/05/2026 14:26:54</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>TEIXEIRA, JOAO - Paranagua 2, PR</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>510180</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>01201578003275</t>
+        </is>
+      </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q129" t="inlineStr"/>
+      <c r="R129" t="inlineStr">
+        <is>
+          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
+        </is>
+      </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>FERTRAN TRANSPORTES LTDA</t>
+        </is>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>5905</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>NÃO (Armazém)</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>TROCA DE NOTA - MOSAIC UBERABA MAP - PLACA: hlk7d71</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>EXPEDIÇÂO MULTITRANS AZ3</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>06/05/2026 14:40:43</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>CONCLUÍDO</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>06/05/2026 14:48:43</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>TEIXEIRA, JOAO - Paranagua 2, PR</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>510181</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>01201578003275</t>
+        </is>
+      </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q130" t="inlineStr"/>
+      <c r="R130" t="inlineStr">
+        <is>
+          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
+        </is>
+      </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>FERTRAN TRANSPORTES LTDA</t>
+        </is>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>5905</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>NÃO (Armazém)</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Troca NF PLACA: ABD-8J70 - MOSAIC X COONAGRO - NP 13-33-00 - GRANEL</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>EXPEDIÇÂO MULTITRANS AZ3</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>07/05/2026 01:03:17</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>300421</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>MULTITRANS TRANSP.ARMAZENS GERAIS LTDA - PR</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>NP 13-33-00</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>5907</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>18740</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>18740</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>CONCLUÍDO</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>07/05/2026 01:20:36</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>VIANA, JOSE - Paranagua 2, PR</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>5822</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>01201578003275</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>84828003000370</t>
+        </is>
+      </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q131" t="inlineStr"/>
+      <c r="R131" t="inlineStr">
+        <is>
+          <t>COONAGRO COOPERATIVA NACIONAL</t>
+        </is>
+      </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>LOGIC TRANSPORTES EIRELI</t>
+        </is>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>5901</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>TROCA DE NOTA - ICL X MOSAIC - PLACA: RUG-7E26</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>EXPEDIÇÃO | MULTITRANS PARANAGUA</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>07/05/2026 05:04:05</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>CONCLUÍDO</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>07/05/2026 05:25:43</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>VIANA, JOSE - Paranagua 2, PR</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>510211</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>01201578000250</t>
+        </is>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q132" t="inlineStr"/>
+      <c r="R132" t="inlineStr">
+        <is>
+          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
+        </is>
+      </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>BELLUNO LOGISTICA E TRANSPORTES BELLUNO LOGISTICA E TRANSPOR</t>
+        </is>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>5905</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>NÃO (Armazém)</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>TROCA DE NOTA - ICL X MOSAIC - PLACA: RUG-7E25</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>EXPEDIÇÃO | MULTITRANS PARANAGUA</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>07/05/2026 05:08:14</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>CONCLUÍDO</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>07/05/2026 05:26:44</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>VIANA, JOSE - Paranagua 2, PR</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>510212</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>01201578000250</t>
+        </is>
+      </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q133" t="inlineStr"/>
+      <c r="R133" t="inlineStr">
+        <is>
+          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
+        </is>
+      </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>BELLUNO LOGISTICA E TRANSPORTES BELLUNO LOGISTICA E TRANSPOR</t>
+        </is>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>5905</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>NÃO (Armazém)</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>TROCA DE NOTA - MOSAIC UBERABA MAP - PLACA: ATR5484</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>EXPEDIÇÂO MULTITRANS AZ3</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>07/05/2026 07:28:58</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>CONCLUÍDO</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>07/05/2026 07:41:24</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>VIANA, JOSE - Paranagua 2, PR</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>510213</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>01201578003275</t>
+        </is>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q134" t="inlineStr"/>
+      <c r="R134" t="inlineStr">
+        <is>
+          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
+        </is>
+      </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>TRANSPORTES RODOVIARIOS VALE DO PIQUIRI LTDA</t>
+        </is>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>5905</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>NÃO (Armazém)</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>TROCA DE NOTA - MOSAIC UBERABA MAP - PLACA: GCV2A53</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>EXPEDIÇÂO MULTITRANS AZ3</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>07/05/2026 07:30:19</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>CONCLUÍDO</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>07/05/2026 07:45:34</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>VIANA, JOSE - Paranagua 2, PR</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>510214</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>01201578003275</t>
+        </is>
+      </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q135" t="inlineStr"/>
+      <c r="R135" t="inlineStr">
+        <is>
+          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
+        </is>
+      </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>G10 TRANSPORTES S A</t>
+        </is>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>5905</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>NÃO (Armazém)</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>TROCA DE NOTA - MOSAIC UBERABA MAP - PLACA: UFU7I62</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>EXPEDIÇÂO MULTITRANS AZ3</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>07/05/2026 07:31:25</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>CONCLUÍDO</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>07/05/2026 07:50:17</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>VIANA, JOSE - Paranagua 2, PR</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>510215</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>01201578003275</t>
+        </is>
+      </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q136" t="inlineStr"/>
+      <c r="R136" t="inlineStr">
+        <is>
+          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
+        </is>
+      </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>FERTRAN TRANSPORTES LTDA</t>
+        </is>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>5905</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>NÃO (Armazém)</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>TROCA DE NOTA - MOSAIC UBERABA MAP - PLACA: BEN8J36</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>EXPEDIÇÂO MULTITRANS AZ3</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>07/05/2026 07:53:34</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q137" t="inlineStr"/>
+      <c r="R137" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>NÃO (Armazém)</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>TROCA DE NOTA - MOSAIC UBERABA MAP - PLACA: BEN8J36</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>EXPEDIÇÂO MULTITRANS AZ3</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>07/05/2026 07:54:30</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>CONCLUÍDO</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>07/05/2026 08:13:00</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>TEIXEIRA, JOAO - Paranagua 2, PR</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>510216</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>01201578003275</t>
+        </is>
+      </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q138" t="inlineStr"/>
+      <c r="R138" t="inlineStr">
+        <is>
+          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
+        </is>
+      </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>RODO M LOGISTICA E SERVICOS LTDA</t>
+        </is>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>5905</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>NÃO (Armazém)</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>TROCA DE NOTA - MOSAIC UBERABA MAP - PLACA: RHG-7A57</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>EXPEDIÇÂO MULTITRANS AZ3</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>06/05/2026 21:18:38</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>CONCLUÍDO</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>06/05/2026 22:52:56</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>RODRIGUES, FERNANDO - Paranagua 2, PR</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q139" t="inlineStr"/>
+      <c r="R139" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>NÃO (Ambos)</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>TROCA DE NOTA - MOSAIC X CTO 1 AGROPECUARIA - PLACA: QCZ-7A13</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>EXPEDIÇÂO MULTITRANS AZ3</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>06/05/2026 21:52:32</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>300389</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>MULTITRANS TRANSP.ARMAZENS GERAIS LTDA - PR</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>KCL 60,5% - CLORETO DE POTASSIO 60,5%, SOL H2O GRANULADO</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>5907</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>48500</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>48500</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>CONCLUÍDO</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>06/05/2026 22:10:48</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>RODRIGUES, FERNANDO - Paranagua 2, PR</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>01201578003275</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>61156501008050</t>
+        </is>
+      </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q140" t="inlineStr"/>
+      <c r="R140" t="inlineStr">
+        <is>
+          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA I</t>
+        </is>
+      </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>NÃO (Assistente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>TROCA DE NOTA - MOSAIC X CTO 1 AGROPECUARIA - PLACA: ATR-5484</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>EXPEDIÇÂO MULTITRANS AZ3</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>06/05/2026 21:56:17</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>300389</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>MULTITRANS TRANSP.ARMAZENS GERAIS LTDA - PR</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>KCL 60,5% - CLORETO DE POTASSIO 60,5%, SOL H2O GRANULADO</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>5907</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>48500</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>48500</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>CONCLUÍDO</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>06/05/2026 22:00:20</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>RODRIGUES, FERNANDO - Paranagua 2, PR</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>01201578003275</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>61156501008050</t>
+        </is>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q141" t="inlineStr"/>
+      <c r="R141" t="inlineStr">
+        <is>
+          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA I</t>
+        </is>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>NÃO (Assistente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>RES: 4° CAMINHÃO TROCA DE NOTA MOSAIC MG X AVANEX INDUSTRIA SC - PLACA QIA6805</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Rosiane Menim dos Santos</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>07/05/2026 00:48:45</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>84052</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>CPA TERMINAL PARANAGUA S.A</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>METANOL</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>6949</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>34580</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>24093861000120</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>02916265013300</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q142" t="inlineStr"/>
+      <c r="R142" t="inlineStr">
+        <is>
+          <t>JBS SA</t>
+        </is>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Troca NF PLACA: AER2118 - MOSAIC X COONAGRO - NP 13-33-00 - GRANEL</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>EXPEDIÇÂO MULTITRANS AZ3</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>07/05/2026 00:54:10</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>300419</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>MULTITRANS TRANSP.ARMAZENS GERAIS LTDA - PR</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>NP 13-33-00</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>5907</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>17600</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>17600</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>CONCLUÍDO</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>07/05/2026 01:19:20</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>VIANA, JOSE - Paranagua 2, PR</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>5821</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>01201578003275</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>84828003000370</t>
+        </is>
+      </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q143" t="inlineStr"/>
+      <c r="R143" t="inlineStr">
+        <is>
+          <t>COONAGRO COOPERATIVA NACIONAL</t>
+        </is>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>LOGIC TRANSPORTES EIRELI</t>
+        </is>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>5901</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>TROCA DE NOTA - MOSAIC UBERABA MAP - PLACA: RXR-9H56</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>EXPEDIÇÂO MULTITRANS AZ3</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>06/05/2026 18:07:52</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>CONCLUÍDO</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>06/05/2026 18:24:03</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>RODRIGUES, FERNANDO - Paranagua 2, PR</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q144" t="inlineStr"/>
+      <c r="R144" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>NÃO (Ambos)</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>TROCA DE NOTA - MOSAIC X CTO 1 AGROPECUARIA - PLACA: SFA-4F26</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>EXPEDIÇÂO MULTITRANS AZ3</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>06/05/2026 18:17:20</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>300356</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>MULTITRANS TRANSP.ARMAZENS GERAIS LTDA - PR</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>KCL 60,5% - CLORETO DE POTASSIO 60,5%, SOL H2O GRANULADO</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>5907</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>48340</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>48340</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>CONCLUÍDO</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>06/05/2026 18:48:03</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>RODRIGUES, FERNANDO - Paranagua 2, PR</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>01201578003275</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>61156501008050</t>
+        </is>
+      </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q145" t="inlineStr"/>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA I</t>
+        </is>
+      </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>NÃO (Assistente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>TROCA DE NOTA - MOSAIC X CTO 1 AGROPECUARIA - PLACA: TBC-5H51</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>EXPEDIÇÂO MULTITRANS AZ3</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>06/05/2026 18:22:28</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>300357</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>MULTITRANS TRANSP.ARMAZENS GERAIS LTDA - PR</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>KCL 60,5% - CLORETO DE POTASSIO 60,5%, SOL H2O GRANULADO</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>5907</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>46640</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>46640</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>CONCLUÍDO</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>06/05/2026 18:49:51</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>RODRIGUES, FERNANDO - Paranagua 2, PR</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>01201578003275</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>61156501008050</t>
+        </is>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q146" t="inlineStr"/>
+      <c r="R146" t="inlineStr">
+        <is>
+          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA I</t>
+        </is>
+      </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>NÃO (Assistente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>TROCA DE NOTA - MOSAIC UBERABA MAP - PLACA: BBJ-5E00</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>EXPEDIÇÂO MULTITRANS AZ3</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>06/05/2026 19:08:40</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>300362</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>MULTITRANS TRANSP.ARMAZENS GERAIS LTDA - PR</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>KCL 60,5% - CLORETO DE POTASSIO 60,5%, SOL H2O GRANULADO</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>5907</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>47860</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>47860</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>CONCLUÍDO</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>06/05/2026 19:20:47</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>RODRIGUES, FERNANDO - Paranagua 2, PR</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>01201578003275</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>61156501008050</t>
+        </is>
+      </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q147" t="inlineStr"/>
+      <c r="R147" t="inlineStr">
+        <is>
+          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA I</t>
+        </is>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>NÃO (Assistente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Troca NF PLACA: AER-2118 - MOSAIC X COONAGRO - NP 13-33-00 - GRANEL</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>EXPEDIÇÂO MULTITRANS AZ3</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>06/05/2026 20:12:59</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>300369</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>MULTITRANS TRANSP.ARMAZENS GERAIS LTDA - PR</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>NP 13-33-00</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>5907</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>16300</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>16300</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>01201578003275</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>61156501008050</t>
+        </is>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q148" t="inlineStr"/>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA I</t>
+        </is>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Re: Troca NF PLACA: AER-2118 - MOSAIC X COONAGRO - NP 13-33-00 - GRANEL</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>EXPEDIÇÂO MULTITRANS AZ3</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>06/05/2026 20:17:32</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>300370</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>MULTITRANS TRANSP.ARMAZENS GERAIS LTDA - PR</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>NP 13-33-00</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>5907</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>14900</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>14900</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>CONCLUÍDO</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>06/05/2026 20:55:44</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>RODRIGUES, FERNANDO - Paranagua 2, PR</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>01201578003275</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>61156501008050</t>
+        </is>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q149" t="inlineStr"/>
+      <c r="R149" t="inlineStr">
+        <is>
+          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA I</t>
+        </is>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>NÃO (Assistente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>TROCA DE NOTA -DESCARGA - PLACA:SLW-2C40</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>EXPEDIÇÃO | MULTITRANS PARANAGUA</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>06/05/2026 20:22:20</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>CONCLUÍDO</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>06/05/2026 21:37:37</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>RODRIGUES, FERNANDO - Paranagua 2, PR</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q150" t="inlineStr"/>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>NÃO (Ambos)</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Troca NF PLACA: ABD-8J70 - MOSAIC X COONAGRO - NP 13-33-00 - GRANEL</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>EXPEDIÇÂO MULTITRANS AZ3</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>06/05/2026 20:23:32</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>300373</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>MULTITRANS TRANSP.ARMAZENS GERAIS LTDA - PR</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>NP 13-33-00</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>5907</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>16440</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>16440</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>CONCLUÍDO</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>06/05/2026 20:56:22</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>RODRIGUES, FERNANDO - Paranagua 2, PR</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>01201578003275</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>61156501008050</t>
+        </is>
+      </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q151" t="inlineStr"/>
+      <c r="R151" t="inlineStr">
+        <is>
+          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA I</t>
+        </is>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>NÃO (Assistente)</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>TROCA DE NOTA -DESCARGA - PLACA:OOM-8F35</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>EXPEDIÇÃO | MULTITRANS PARANAGUA</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>06/05/2026 20:25:26</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>CONCLUÍDO</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>06/05/2026 21:49:05</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>RODRIGUES, FERNANDO - Paranagua 2, PR</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q152" t="inlineStr"/>
+      <c r="R152" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>NÃO (Ambos)</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>TROCA DE NOTA -DESCARGA - PLACA: AZG-0F40</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>EXPEDIÇÃO | MULTITRANS</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>06/05/2026 20:31:14</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>CONCLUÍDO</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>06/05/2026 21:57:45</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>RODRIGUES, FERNANDO - Paranagua 2, PR</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q153" t="inlineStr"/>
+      <c r="R153" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>NÃO (Ambos)</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>TROCA DE NOTA - ICL X MOSAIC - PLACA: TPP 3E02</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>EXPEDIÇÃO | MULTITRANS</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>07/05/2026 08:15:10</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>141537</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>ICL America do Sul S.A</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>INFINITY NEW FERT NPK 02-18 GRAN GRANEL</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>6119</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>46740</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>CONCLUÍDO</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>07/05/2026 09:38:47</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>TEIXEIRA, JOAO - Paranagua 2, PR</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>510218</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>60398138000546</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>01201578000250</t>
+        </is>
+      </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q154" t="inlineStr"/>
+      <c r="R154" t="inlineStr">
+        <is>
+          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
+        </is>
+      </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>RODOFROTA TRANSPORTES RODOVIARIOS E LOGISTICA LTDA</t>
+        </is>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>5905</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>TROCA DE NOTA - MOSAIC UBERABA MAP - PLACA: GDC9J98</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>EXPEDIÇÂO MULTITRANS AZ3</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>07/05/2026 08:57:01</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>CONCLUÍDO</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>07/05/2026 09:49:11</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>TEIXEIRA, JOAO - Paranagua 2, PR</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>510219</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>01201578003275</t>
+        </is>
+      </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q155" t="inlineStr"/>
+      <c r="R155" t="inlineStr">
+        <is>
+          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
+        </is>
+      </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>G10 TRANSPORTES S A</t>
+        </is>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>5905</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>NÃO (Armazém)</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>TROCA DE NOTA - MOSAIC UBERABA MAP - PLACA: GCV2A25</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>EXPEDIÇÂO MULTITRANS AZ3</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>07/05/2026 09:04:41</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>CONCLUÍDO</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>07/05/2026 09:49:56</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>TEIXEIRA, JOAO - Paranagua 2, PR</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>510220</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>01201578003275</t>
+        </is>
+      </c>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q156" t="inlineStr"/>
+      <c r="R156" t="inlineStr">
+        <is>
+          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
+        </is>
+      </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>G10 TRANSPORTES S A</t>
+        </is>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>5905</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>NÃO (Armazém)</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>TROCA DE NFE PLACA ELY-1E72 - O.V: 30508727 - VARREDURA</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>EXPEDIÇÃO | MULTITRANS PARANAGUA</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>07/05/2026 14:35:40</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>691070</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>MULTITRANS TRANSP.ARMAZENS GERAIS LTDA - PR</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>VARREDURA</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>5907</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>11080</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>11080</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>CONCLUÍDO</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>07/05/2026 14:48:35</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>TEIXEIRA, JOAO - Paranagua 2, PR</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>5827</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>01201578000250</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>88032876987</t>
+        </is>
+      </c>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q157" t="inlineStr"/>
+      <c r="R157" t="inlineStr">
+        <is>
+          <t>EDIRLEI CESAR ANTUNES</t>
+        </is>
+      </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>LOGAPORTO LOGISTICA PORTUARIA LTDA</t>
+        </is>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>5101</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>TROCA DE NFE PLACA : FIM-0H96 - O.V: 30508727 - VARREDURA</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>EXPEDIÇÃO | MULTITRANS</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>07/05/2026 15:27:50</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>691076</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>MULTITRANS TRANSP.ARMAZENS GERAIS LTDA - PR</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>VARREDURA</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>5907</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>3290</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>3290</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>CONCLUÍDO</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>07/05/2026 15:41:38</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>TEIXEIRA, JOAO - Paranagua 2, PR</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>5828</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>01201578000250</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>88032876987</t>
+        </is>
+      </c>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q158" t="inlineStr"/>
+      <c r="R158" t="inlineStr">
+        <is>
+          <t>EDIRLEI CESAR ANTUNES</t>
+        </is>
+      </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>LOGAPORTO LOGISTICA PORTUARIA LTDA</t>
+        </is>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>5101</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>TROCA DE NOTA - MOSAIC X CTO 1 AGROPECUARIA - PLACA: BEQ-3C67</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>EXPEDIÇÂO MULTITRANS AZ3</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>07/05/2026 15:35:14</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>300476</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>MULTITRANS TRANSP.ARMAZENS GERAIS LTDA - PR</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>KCL 60,5% - CLORETO DE POTASSIO 60,5%, SOL H2O GRANULADO</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>5907</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>47620</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>47620</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>01201578003275</t>
+        </is>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>61156501008050</t>
+        </is>
+      </c>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q159" t="inlineStr"/>
+      <c r="R159" t="inlineStr">
+        <is>
+          <t>MOSAIC FERTILIZANTES DO BRASIL LTDA - PARANAGUA I</t>
+        </is>
+      </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>TROCA DE NOTA - PLACA: AQZ0D60</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Portaria</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>07/05/2026 12:51:11</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>377778</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>FORTESOLO SERVICOS INTEGRADOS S.A.</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>SSP - Super simples 18,5%</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>5907</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>31460</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>CONCLUÍDO</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>07/05/2026 13:58:49</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>TEIXEIRA, JOAO - Paranagua 2, PR</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>5826</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>80276314000150</t>
+        </is>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>84828003000370</t>
+        </is>
+      </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q160" t="inlineStr"/>
+      <c r="R160" t="inlineStr">
+        <is>
+          <t>COONAGRO COOPERATIVA NACIONAL</t>
+        </is>
+      </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>LOGIC TRANSPORTES EIRELI</t>
+        </is>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>5901</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>TROCA DE NOTA - MOSAIC UBERABA MAP - PLACA: SFH1A50</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>EXPEDIÇÂO MULTITRANS AZ3</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>07/05/2026 13:19:46</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>CONCLUÍDO</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>07/05/2026 14:20:10</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>TEIXEIRA, JOAO - Paranagua 2, PR</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>510223</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>01201578003275</t>
+        </is>
+      </c>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q161" t="inlineStr"/>
+      <c r="R161" t="inlineStr">
+        <is>
+          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
+        </is>
+      </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>TRANSPORTADORA BOA VIAGEM LTDA</t>
+        </is>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>5905</t>
+        </is>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>NÃO (Armazém)</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>TROCA DE NOTA - MOSAIC UBERABA MAP - PLACA: dbm4314</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>EXPEDIÇÂO MULTITRANS AZ3</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>07/05/2026 13:21:00</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>CONCLUÍDO</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>07/05/2026 14:20:28</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>TEIXEIRA, JOAO - Paranagua 2, PR</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>510224</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>01201578003275</t>
+        </is>
+      </c>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q162" t="inlineStr"/>
+      <c r="R162" t="inlineStr">
+        <is>
+          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
+        </is>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>AGROLOG TRANSPORT CARGAS GERAL LTDA</t>
+        </is>
+      </c>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>5905</t>
+        </is>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>NÃO (Armazém)</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>TROCA DE NOTA - MOSAIC UBERABA MAP - PLACA: qxb2i63</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>EXPEDIÇÂO MULTITRANS AZ3</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>07/05/2026 13:22:15</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>CONCLUÍDO</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>07/05/2026 14:20:47</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>TEIXEIRA, JOAO - Paranagua 2, PR</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>510225</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>01201578003275</t>
+        </is>
+      </c>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q163" t="inlineStr"/>
+      <c r="R163" t="inlineStr">
+        <is>
+          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
+        </is>
+      </c>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>RODOFROTA TRANSPORTES RODOVIARIOS E LOGISTICA LTDA</t>
+        </is>
+      </c>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>5905</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>NÃO (Armazém)</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>TROCA DE NOTA - MOSAIC UBERABA MAP - PLACA: avr5f40</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>EXPEDIÇÂO MULTITRANS AZ3</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>07/05/2026 13:24:51</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>CONCLUÍDO</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>07/05/2026 14:21:08</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>TEIXEIRA, JOAO - Paranagua 2, PR</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>510226</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>01201578003275</t>
+        </is>
+      </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q164" t="inlineStr"/>
+      <c r="R164" t="inlineStr">
+        <is>
+          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
+        </is>
+      </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>TRANSPORTADORA BOA VIAGEM LTDA</t>
+        </is>
+      </c>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>5905</t>
+        </is>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>NÃO (Armazém)</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>TROCA DE NOTA - ICL X MOSAIC - PLACA: QIY-6G81</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>EXPEDIÇÃO | MULTITRANS PARANAGUA</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>07/05/2026 13:37:40</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>141535</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>ICL America do Sul S.A</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>INFINITY NEW FERT NPK 02-18 GRAN GRANEL</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>6923</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>48000</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>CONCLUÍDO</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>07/05/2026 14:30:07</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>TEIXEIRA, JOAO - Paranagua 2, PR</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>510227</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>60398138000546</t>
+        </is>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>01201578000250</t>
+        </is>
+      </c>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q165" t="inlineStr"/>
+      <c r="R165" t="inlineStr">
+        <is>
+          <t>MULTITRANS TRANSP E ARMAZENS GERAIS</t>
+        </is>
+      </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>RODOFROTA TRANSPORTES RODOVIARIOS E LOGISTICA LTDA</t>
+        </is>
+      </c>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>5905</t>
+        </is>
+      </c>
+      <c r="U165" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
